--- a/data/supplementary_tables/Supplementary Table 17.xlsx
+++ b/data/supplementary_tables/Supplementary Table 17.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Eukaryotes_Asgard_TACK/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Nature_submission_verified_red/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD299220-DD7A-5E44-A500-D6DA35B2BDB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AA0CB23-FB8F-5E41-BE76-2AB8084DE044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="17420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="164">
   <si>
     <t>Protein_Short_Name</t>
   </si>
@@ -67,9 +67,6 @@
     <t>MCM family</t>
   </si>
   <si>
-    <t>Catalyzes the hydrolysis of the</t>
-  </si>
-  <si>
     <t>Phosphatase</t>
   </si>
   <si>
@@ -97,9 +94,6 @@
     <t>Function in general translation initiation</t>
   </si>
   <si>
-    <t>Binds to 23S rRNA.</t>
-  </si>
-  <si>
     <t>Sliding clamp subunit</t>
   </si>
   <si>
@@ -121,18 +115,6 @@
     <t>PDCD5 family</t>
   </si>
   <si>
-    <t>Large family of predicted...</t>
-  </si>
-  <si>
-    <t>COMPASS (Set1C) complex that specifically</t>
-  </si>
-  <si>
-    <t>Binds 16S rRNA</t>
-  </si>
-  <si>
-    <t>Catalyzes the last two sequential</t>
-  </si>
-  <si>
     <t>Archaeal Rpom Eukaryotic RPA12 RPB9</t>
   </si>
   <si>
@@ -160,12 +142,6 @@
     <t>Serine Threonine Protein Kinase</t>
   </si>
   <si>
-    <t>Gamma-secretase Complex, An Endoprotease...</t>
-  </si>
-  <si>
-    <t>Probable Brix domain-containing ribosomal...</t>
-  </si>
-  <si>
     <t>'Cold-shock' DNA-binding domain</t>
   </si>
   <si>
@@ -181,21 +157,12 @@
     <t>Pantothenate kinase</t>
   </si>
   <si>
-    <t>Predicted SAM-dependent RNA...</t>
-  </si>
-  <si>
     <t>Sodium/hydrogen exchanger family</t>
   </si>
   <si>
     <t>Eukaryotic Ribosomal Protein El14 Family</t>
   </si>
   <si>
-    <t>Could be</t>
-  </si>
-  <si>
-    <t>Dual specificity protein phosphatase,...</t>
-  </si>
-  <si>
     <t>60S ribosome subunit biogenesis protein</t>
   </si>
   <si>
@@ -214,21 +181,12 @@
     <t>Molecular chaperone capable of stabilizing</t>
   </si>
   <si>
-    <t>Uptake of acetate and succinate.</t>
-  </si>
-  <si>
     <t>Enzyme 2</t>
   </si>
   <si>
     <t>Sulphite efflux pump</t>
   </si>
   <si>
-    <t>Mannose-6-phosphate Isomerase Type 2...</t>
-  </si>
-  <si>
-    <t>Haloacid dehalogenase domain protein...</t>
-  </si>
-  <si>
     <t>Non-catalytic component of the exosome</t>
   </si>
   <si>
@@ -238,21 +196,12 @@
     <t>Carbonic anhydrase</t>
   </si>
   <si>
-    <t>Catalyzes the reversible transfer of</t>
-  </si>
-  <si>
     <t>Binds to the 23S rRNA</t>
   </si>
   <si>
-    <t>Binds directly to 23S rRNA.</t>
-  </si>
-  <si>
     <t>Catalyzes the phosphorylation of fructose</t>
   </si>
   <si>
-    <t>LDH MDH superfamily.</t>
-  </si>
-  <si>
     <t>Arrestin domain-containing protein 3</t>
   </si>
   <si>
@@ -274,9 +223,6 @@
     <t>Zinc Transporter</t>
   </si>
   <si>
-    <t>Protein N-acetylglucosaminyltransferase...</t>
-  </si>
-  <si>
     <t>Methyltransferase</t>
   </si>
   <si>
@@ -292,9 +238,6 @@
     <t>Serine threonine-protein phosphatase</t>
   </si>
   <si>
-    <t>Catalyzes the GTP-dependent ribosomal...</t>
-  </si>
-  <si>
     <t>COG5524 Bacteriorhodopsin</t>
   </si>
   <si>
@@ -316,9 +259,6 @@
     <t>Exodeoxyribonuclease III</t>
   </si>
   <si>
-    <t>S-adenosyl-L-methionine-dependent...</t>
-  </si>
-  <si>
     <t>Solute carrier family 41</t>
   </si>
   <si>
@@ -328,9 +268,6 @@
     <t>Endonuclease Activity</t>
   </si>
   <si>
-    <t>Catalyzes the ATP-dependent...</t>
-  </si>
-  <si>
     <t>COG1061 DNA or RNA helicases</t>
   </si>
   <si>
@@ -373,12 +310,6 @@
     <t>Reversibly transfers an adenylyl group</t>
   </si>
   <si>
-    <t>It is</t>
-  </si>
-  <si>
-    <t>Vacuolar protein sorting-associated...</t>
-  </si>
-  <si>
     <t>Catalyzes the attachment of tyrosine</t>
   </si>
   <si>
@@ -391,9 +322,6 @@
     <t>Binds double-stranded DNA tightly but</t>
   </si>
   <si>
-    <t>Fibronectin type III domain-containing...</t>
-  </si>
-  <si>
     <t>Mature Ribosome Assembly</t>
   </si>
   <si>
@@ -433,9 +361,6 @@
     <t>U6 snRNA-associated Sm-like protein</t>
   </si>
   <si>
-    <t>Sodium Neurotransmitter Symporter (snf)...</t>
-  </si>
-  <si>
     <t>Ribosomal Protein S15</t>
   </si>
   <si>
@@ -475,24 +400,15 @@
     <t>Oxidoreductase Activity</t>
   </si>
   <si>
-    <t>Methenyltetrahydrofolate Synthetase...</t>
-  </si>
-  <si>
     <t>Catalyzes the attachment of glycine</t>
   </si>
   <si>
-    <t>Structure-specific nuclease with 5'-flap...</t>
-  </si>
-  <si>
     <t>Catalyzes the conversion of 3'-phosphate</t>
   </si>
   <si>
     <t>Cell Adhesion</t>
   </si>
   <si>
-    <t>Stabilizes TBP binding to an</t>
-  </si>
-  <si>
     <t>Necrosis inducing protein (NPP1)</t>
   </si>
   <si>
@@ -506,6 +422,96 @@
   </si>
   <si>
     <t>Supplementary Table 17 | ESP short names in DPANN archaea: aggregated genome detection counts before and after decontamination and corresponding loss rates</t>
+  </si>
+  <si>
+    <t>Nucleotide-binding domain protein</t>
+  </si>
+  <si>
+    <t>γ-secretase subunit</t>
+  </si>
+  <si>
+    <t>Brix domain-containing ribosome biogenesis protein</t>
+  </si>
+  <si>
+    <t>SAM-dependent RNA methyltransferase</t>
+  </si>
+  <si>
+    <t>Dual-specificity phosphatase</t>
+  </si>
+  <si>
+    <t>Mannose-6-phosphate isomerase</t>
+  </si>
+  <si>
+    <t>HAD hydrolase</t>
+  </si>
+  <si>
+    <t>Protein GlcNAc transferase activity</t>
+  </si>
+  <si>
+    <t>Catalyzes GTP-dependent ribosomal translocation during translation elongation</t>
+  </si>
+  <si>
+    <t>Diphthine synthase</t>
+  </si>
+  <si>
+    <t>TYW3</t>
+  </si>
+  <si>
+    <t>Catalyzes ATP-dependent 4-O phosphorylation of Kdo-lipid IV(A)</t>
+  </si>
+  <si>
+    <t>VPS-associated protein</t>
+  </si>
+  <si>
+    <t>FNIII domain-containing protein 2</t>
+  </si>
+  <si>
+    <t>SNF family transporter</t>
+  </si>
+  <si>
+    <t>MTHFS</t>
+  </si>
+  <si>
+    <t>5′-flap endonuclease involved in DNA replication and repair</t>
+  </si>
+  <si>
+    <t>Hydrolyzes reactive intermediates of riboflavin biosynthesis</t>
+  </si>
+  <si>
+    <t>Ribosomal protein L24</t>
+  </si>
+  <si>
+    <t>Ribosomal protein L14</t>
+  </si>
+  <si>
+    <t>Ribosomal protein S4</t>
+  </si>
+  <si>
+    <t>Catalytic subunit of the COMPASS complex that methylates H3K4</t>
+  </si>
+  <si>
+    <t>GlmU</t>
+  </si>
+  <si>
+    <t>tRNA pseudouridine synthase</t>
+  </si>
+  <si>
+    <t>Acetate/succinate transporter</t>
+  </si>
+  <si>
+    <t>Catalyzes reversible phosphate transfer between ATP and AMP</t>
+  </si>
+  <si>
+    <t>Ribosomal protein L1</t>
+  </si>
+  <si>
+    <t>LDH MDH superfamily</t>
+  </si>
+  <si>
+    <t>Involved in cell adhesion</t>
+  </si>
+  <si>
+    <t>Stabilizes TBP binding and recruits RNA polymerase to the pre-initiation complex</t>
   </si>
 </sst>
 </file>
@@ -878,7 +884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D160"/>
+  <dimension ref="A1:D162"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="27" style="1" customWidth="1"/>
@@ -890,7 +896,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -1063,7 +1069,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>151</v>
       </c>
       <c r="B14" s="1">
         <v>4</v>
@@ -1077,7 +1083,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" s="1">
         <v>10</v>
@@ -1091,7 +1097,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" s="1">
         <v>5</v>
@@ -1105,7 +1111,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" s="1">
         <v>5</v>
@@ -1119,7 +1125,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" s="1">
         <v>14</v>
@@ -1133,7 +1139,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" s="1">
         <v>7</v>
@@ -1147,7 +1153,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20" s="1">
         <v>22</v>
@@ -1161,7 +1167,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" s="1">
         <v>10</v>
@@ -1175,7 +1181,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" s="1">
         <v>10</v>
@@ -1189,7 +1195,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" s="1">
         <v>31</v>
@@ -1203,83 +1209,83 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>25</v>
+        <v>152</v>
       </c>
       <c r="B24" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C24" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D24" s="5">
-        <v>6.25</v>
+        <v>6.6666666666666696</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
-        <v>26</v>
+        <v>153</v>
       </c>
       <c r="B25" s="1">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C25" s="1">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D25" s="5">
-        <v>5.8823529411764701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B26" s="1">
-        <v>620</v>
+        <v>17</v>
       </c>
       <c r="C26" s="1">
-        <v>603</v>
+        <v>16</v>
       </c>
       <c r="D26" s="5">
-        <v>2.7419354838709702</v>
+        <v>5.8823529411764701</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B27" s="1">
-        <v>23</v>
+        <v>620</v>
       </c>
       <c r="C27" s="1">
-        <v>22</v>
+        <v>603</v>
       </c>
       <c r="D27" s="5">
-        <v>4.3478260869565197</v>
+        <v>2.7419354838709702</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B28" s="1">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="C28" s="1">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="D28" s="5">
-        <v>3.4482758620689702</v>
+        <v>4.3478260869565197</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B29" s="1">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="C29" s="1">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="D29" s="5">
         <v>3.4482758620689702</v>
@@ -1287,91 +1293,91 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B30" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C30" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D30" s="5">
-        <v>3.3333333333333299</v>
+        <v>3.4482758620689702</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B31" s="1">
-        <v>294</v>
+        <v>30</v>
       </c>
       <c r="C31" s="1">
-        <v>287</v>
+        <v>29</v>
       </c>
       <c r="D31" s="5">
-        <v>2.38095238095238</v>
+        <v>3.3333333333333299</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B32" s="1">
-        <v>199</v>
+        <v>294</v>
       </c>
       <c r="C32" s="1">
-        <v>195</v>
+        <v>287</v>
       </c>
       <c r="D32" s="5">
-        <v>2.0100502512562799</v>
+        <v>2.38095238095238</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
-        <v>34</v>
+        <v>134</v>
       </c>
       <c r="B33" s="1">
-        <v>52</v>
+        <v>199</v>
       </c>
       <c r="C33" s="1">
-        <v>51</v>
+        <v>195</v>
       </c>
       <c r="D33" s="5">
-        <v>1.92307692307692</v>
+        <v>2.0100502512562799</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
-        <v>35</v>
+        <v>155</v>
       </c>
       <c r="B34" s="1">
-        <v>313</v>
+        <v>52</v>
       </c>
       <c r="C34" s="1">
-        <v>307</v>
+        <v>51</v>
       </c>
       <c r="D34" s="5">
-        <v>1.91693290734824</v>
+        <v>1.92307692307692</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
-        <v>36</v>
+        <v>154</v>
       </c>
       <c r="B35" s="1">
-        <v>62</v>
+        <v>313</v>
       </c>
       <c r="C35" s="1">
-        <v>61</v>
+        <v>307</v>
       </c>
       <c r="D35" s="5">
-        <v>1.61290322580645</v>
+        <v>1.91693290734824</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
-        <v>37</v>
+        <v>156</v>
       </c>
       <c r="B36" s="1">
         <v>62</v>
@@ -1385,83 +1391,83 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B37" s="1">
-        <v>173</v>
+        <v>62</v>
       </c>
       <c r="C37" s="1">
-        <v>171</v>
+        <v>61</v>
       </c>
       <c r="D37" s="5">
-        <v>1.15606936416185</v>
+        <v>1.61290322580645</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B38" s="1">
-        <v>94</v>
+        <v>173</v>
       </c>
       <c r="C38" s="1">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="D38" s="5">
-        <v>1.0638297872340401</v>
+        <v>1.15606936416185</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B39" s="1">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C39" s="1">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D39" s="5">
-        <v>1</v>
+        <v>1.0638297872340401</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B40" s="1">
-        <v>239</v>
+        <v>100</v>
       </c>
       <c r="C40" s="1">
-        <v>237</v>
+        <v>99</v>
       </c>
       <c r="D40" s="5">
-        <v>0.836820083682008</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B41" s="1">
-        <v>179</v>
+        <v>239</v>
       </c>
       <c r="C41" s="1">
-        <v>179</v>
+        <v>237</v>
       </c>
       <c r="D41" s="5">
-        <v>0</v>
+        <v>0.836820083682008</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B42" s="1">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="C42" s="1">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="D42" s="5">
         <v>0</v>
@@ -1469,13 +1475,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B43" s="1">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="C43" s="1">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D43" s="5">
         <v>0</v>
@@ -1483,13 +1489,13 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B44" s="1">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C44" s="1">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D44" s="5">
         <v>0</v>
@@ -1497,13 +1503,13 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B45" s="1">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="C45" s="1">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="D45" s="5">
         <v>0</v>
@@ -1511,13 +1517,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
-        <v>47</v>
+        <v>135</v>
       </c>
       <c r="B46" s="1">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C46" s="1">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="D46" s="5">
         <v>0</v>
@@ -1525,13 +1531,13 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="B47" s="1">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C47" s="1">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D47" s="5">
         <v>0</v>
@@ -1539,13 +1545,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B48" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C48" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D48" s="5">
         <v>0</v>
@@ -1553,13 +1559,13 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B49" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C49" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D49" s="5">
         <v>0</v>
@@ -1567,13 +1573,13 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B50" s="1">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C50" s="1">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D50" s="5">
         <v>0</v>
@@ -1581,13 +1587,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B51" s="1">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C51" s="1">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D51" s="5">
         <v>0</v>
@@ -1595,13 +1601,13 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B52" s="1">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C52" s="1">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D52" s="5">
         <v>0</v>
@@ -1609,7 +1615,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
-        <v>54</v>
+        <v>137</v>
       </c>
       <c r="B53" s="1">
         <v>18</v>
@@ -1623,7 +1629,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B54" s="1">
         <v>18</v>
@@ -1637,13 +1643,13 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B55" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C55" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D55" s="5">
         <v>0</v>
@@ -1651,13 +1657,13 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
-        <v>57</v>
+        <v>157</v>
       </c>
       <c r="B56" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C56" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D56" s="5">
         <v>0</v>
@@ -1665,7 +1671,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="B57" s="1">
         <v>15</v>
@@ -1679,13 +1685,13 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="B58" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C58" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D58" s="5">
         <v>0</v>
@@ -1693,13 +1699,13 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B59" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C59" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D59" s="5">
         <v>0</v>
@@ -1707,13 +1713,13 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B60" s="1">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C60" s="1">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D60" s="5">
         <v>0</v>
@@ -1721,7 +1727,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B61" s="1">
         <v>13</v>
@@ -1735,7 +1741,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B62" s="1">
         <v>13</v>
@@ -1749,13 +1755,13 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B63" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C63" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D63" s="5">
         <v>0</v>
@@ -1763,13 +1769,13 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
-        <v>65</v>
+        <v>158</v>
       </c>
       <c r="B64" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C64" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D64" s="5">
         <v>0</v>
@@ -1777,13 +1783,13 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="B65" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C65" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D65" s="5">
         <v>0</v>
@@ -1791,13 +1797,13 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="B66" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C66" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D66" s="5">
         <v>0</v>
@@ -1805,13 +1811,13 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
-        <v>68</v>
+        <v>139</v>
       </c>
       <c r="B67" s="1">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C67" s="1">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D67" s="5">
         <v>0</v>
@@ -1819,13 +1825,13 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
-        <v>69</v>
+        <v>140</v>
       </c>
       <c r="B68" s="1">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C68" s="1">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D68" s="5">
         <v>0</v>
@@ -1833,13 +1839,13 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B69" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C69" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D69" s="5">
         <v>0</v>
@@ -1847,7 +1853,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="B70" s="1">
         <v>6</v>
@@ -1861,7 +1867,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B71" s="1">
         <v>6</v>
@@ -1875,7 +1881,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
       <c r="B72" s="1">
         <v>6</v>
@@ -1889,7 +1895,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="B73" s="1">
         <v>6</v>
@@ -1903,13 +1909,13 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="B74" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C74" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D74" s="5">
         <v>0</v>
@@ -1917,7 +1923,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="B75" s="1">
         <v>5</v>
@@ -1931,7 +1937,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
-        <v>77</v>
+        <v>161</v>
       </c>
       <c r="B76" s="1">
         <v>5</v>
@@ -1945,13 +1951,13 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A77" s="1" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="B77" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C77" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D77" s="5">
         <v>0</v>
@@ -1959,7 +1965,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A78" s="1" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="B78" s="1">
         <v>4</v>
@@ -1973,7 +1979,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A79" s="1" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="B79" s="1">
         <v>4</v>
@@ -1987,13 +1993,13 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A80" s="1" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="B80" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C80" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D80" s="5">
         <v>0</v>
@@ -2001,13 +2007,13 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A81" s="1" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="B81" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C81" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D81" s="5">
         <v>0</v>
@@ -2015,7 +2021,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A82" s="1" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B82" s="1">
         <v>4</v>
@@ -2029,7 +2035,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A83" s="1" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="B83" s="1">
         <v>4</v>
@@ -2043,13 +2049,13 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A84" s="1" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="B84" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C84" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D84" s="5">
         <v>0</v>
@@ -2057,7 +2063,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A85" s="1" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="B85" s="1">
         <v>3</v>
@@ -2071,13 +2077,13 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A86" s="1" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="B86" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C86" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D86" s="5">
         <v>0</v>
@@ -2085,13 +2091,13 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A87" s="1" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="B87" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C87" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D87" s="5">
         <v>0</v>
@@ -2099,7 +2105,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A88" s="1" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="B88" s="1">
         <v>3</v>
@@ -2113,7 +2119,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A89" s="1" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="B89" s="1">
         <v>3</v>
@@ -2127,7 +2133,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A90" s="1" t="s">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="B90" s="1">
         <v>3</v>
@@ -2141,7 +2147,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A91" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="B91" s="1">
         <v>3</v>
@@ -2155,7 +2161,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A92" s="1" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B92" s="1">
         <v>3</v>
@@ -2169,7 +2175,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B93" s="1">
         <v>3</v>
@@ -2183,7 +2189,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="B94" s="1">
         <v>3</v>
@@ -2197,7 +2203,7 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="B95" s="1">
         <v>3</v>
@@ -2211,7 +2217,7 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A96" s="1" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="B96" s="1">
         <v>3</v>
@@ -2225,13 +2231,13 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A97" s="1" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="B97" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C97" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D97" s="5">
         <v>0</v>
@@ -2239,7 +2245,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="B98" s="1">
         <v>3</v>
@@ -2253,13 +2259,13 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="B99" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C99" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D99" s="5">
         <v>0</v>
@@ -2267,13 +2273,13 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="B100" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C100" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D100" s="5">
         <v>0</v>
@@ -2281,13 +2287,13 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="B101" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C101" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D101" s="5">
         <v>0</v>
@@ -2295,7 +2301,7 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="B102" s="1">
         <v>2</v>
@@ -2309,7 +2315,7 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A103" s="1" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="B103" s="1">
         <v>2</v>
@@ -2323,7 +2329,7 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A104" s="1" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="B104" s="1">
         <v>2</v>
@@ -2337,7 +2343,7 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A105" s="1" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="B105" s="1">
         <v>2</v>
@@ -2351,7 +2357,7 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A106" s="1" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="B106" s="1">
         <v>2</v>
@@ -2365,7 +2371,7 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A107" s="1" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="B107" s="1">
         <v>2</v>
@@ -2379,7 +2385,7 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A108" s="1" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="B108" s="1">
         <v>2</v>
@@ -2393,7 +2399,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A109" s="1" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="B109" s="1">
         <v>2</v>
@@ -2407,7 +2413,7 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A110" s="1" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="B110" s="1">
         <v>2</v>
@@ -2421,7 +2427,7 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A111" s="1" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="B111" s="1">
         <v>2</v>
@@ -2435,13 +2441,13 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A112" s="1" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="B112" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C112" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D112" s="5">
         <v>0</v>
@@ -2449,13 +2455,13 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A113" s="1" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="B113" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C113" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D113" s="5">
         <v>0</v>
@@ -2463,7 +2469,7 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A114" s="1" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="B114" s="1">
         <v>1</v>
@@ -2477,7 +2483,7 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A115" s="1" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="B115" s="1">
         <v>1</v>
@@ -2491,7 +2497,7 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A116" s="1" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="B116" s="1">
         <v>1</v>
@@ -2505,7 +2511,7 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A117" s="1" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="B117" s="1">
         <v>1</v>
@@ -2519,7 +2525,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A118" s="1" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="B118" s="1">
         <v>1</v>
@@ -2533,7 +2539,7 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A119" s="1" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="B119" s="1">
         <v>1</v>
@@ -2547,7 +2553,7 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A120" s="1" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="B120" s="1">
         <v>1</v>
@@ -2561,7 +2567,7 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A121" s="1" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B121" s="1">
         <v>1</v>
@@ -2575,13 +2581,13 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A122" s="1" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="B122" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C122" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D122" s="5">
         <v>0</v>
@@ -2589,7 +2595,7 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A123" s="1" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="B123" s="1">
         <v>1</v>
@@ -2603,13 +2609,13 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A124" s="1" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B124" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C124" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D124" s="5">
         <v>0</v>
@@ -2617,7 +2623,7 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A125" s="1" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="B125" s="1">
         <v>1</v>
@@ -2631,7 +2637,7 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A126" s="1" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="B126" s="1">
         <v>1</v>
@@ -2645,7 +2651,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A127" s="1" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="B127" s="1">
         <v>1</v>
@@ -2659,7 +2665,7 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A128" s="1" t="s">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="B128" s="1">
         <v>1</v>
@@ -2673,7 +2679,7 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A129" s="1" t="s">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="B129" s="1">
         <v>1</v>
@@ -2687,7 +2693,7 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A130" s="1" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="B130" s="1">
         <v>1</v>
@@ -2701,7 +2707,7 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A131" s="1" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="B131" s="1">
         <v>1</v>
@@ -2715,7 +2721,7 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A132" s="1" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="B132" s="1">
         <v>1</v>
@@ -2729,7 +2735,7 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A133" s="1" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="B133" s="1">
         <v>1</v>
@@ -2743,7 +2749,7 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A134" s="1" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="B134" s="1">
         <v>1</v>
@@ -2757,7 +2763,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A135" s="1" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="B135" s="1">
         <v>1</v>
@@ -2771,7 +2777,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A136" s="1" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="B136" s="1">
         <v>1</v>
@@ -2785,7 +2791,7 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A137" s="1" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="B137" s="1">
         <v>1</v>
@@ -2799,7 +2805,7 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A138" s="1" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="B138" s="1">
         <v>1</v>
@@ -2813,7 +2819,7 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A139" s="1" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B139" s="1">
         <v>1</v>
@@ -2827,7 +2833,7 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A140" s="1" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="B140" s="1">
         <v>1</v>
@@ -2841,7 +2847,7 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A141" s="1" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="B141" s="1">
         <v>1</v>
@@ -2855,7 +2861,7 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A142" s="1" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="B142" s="1">
         <v>1</v>
@@ -2869,7 +2875,7 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A143" s="1" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="B143" s="1">
         <v>1</v>
@@ -2883,7 +2889,7 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A144" s="1" t="s">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="B144" s="1">
         <v>1</v>
@@ -2897,7 +2903,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A145" s="1" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="B145" s="1">
         <v>1</v>
@@ -2911,7 +2917,7 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A146" s="1" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="B146" s="1">
         <v>1</v>
@@ -2925,7 +2931,7 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A147" s="1" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="B147" s="1">
         <v>1</v>
@@ -2939,7 +2945,7 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A148" s="1" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="B148" s="1">
         <v>1</v>
@@ -2953,7 +2959,7 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A149" s="1" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="B149" s="1">
         <v>1</v>
@@ -2967,7 +2973,7 @@
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A150" s="1" t="s">
-        <v>150</v>
+        <v>123</v>
       </c>
       <c r="B150" s="1">
         <v>1</v>
@@ -2981,7 +2987,7 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A151" s="1" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="B151" s="1">
         <v>1</v>
@@ -2995,7 +3001,7 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A152" s="1" t="s">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="B152" s="1">
         <v>1</v>
@@ -3009,7 +3015,7 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A153" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B153" s="1">
         <v>1</v>
@@ -3023,7 +3029,7 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A154" s="1" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="B154" s="1">
         <v>1</v>
@@ -3037,7 +3043,7 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A155" s="1" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B155" s="1">
         <v>1</v>
@@ -3051,7 +3057,7 @@
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A156" s="1" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="B156" s="1">
         <v>1</v>
@@ -3065,7 +3071,7 @@
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A157" s="1" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="B157" s="1">
         <v>1</v>
@@ -3079,7 +3085,7 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A158" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B158" s="1">
         <v>1</v>
@@ -3091,21 +3097,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B159" s="4">
-        <v>1</v>
-      </c>
-      <c r="C159" s="4">
-        <v>1</v>
-      </c>
-      <c r="D159" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.15"/>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A159" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B159" s="1">
+        <v>1</v>
+      </c>
+      <c r="C159" s="1">
+        <v>1</v>
+      </c>
+      <c r="D159" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A160" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B160" s="1">
+        <v>1</v>
+      </c>
+      <c r="C160" s="1">
+        <v>1</v>
+      </c>
+      <c r="D160" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B161" s="4">
+        <v>1</v>
+      </c>
+      <c r="C161" s="4">
+        <v>1</v>
+      </c>
+      <c r="D161" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
